--- a/htr-Mapping-CDA-FHIR/ig/mappingAssociationPrescriptionCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingAssociationPrescriptionCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-14T14:13:57+00:00</t>
+    <t>2025-05-20T08:55:00+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingAssociationPrescriptionCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingAssociationPrescriptionCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-20T08:55:00+00:00</t>
+    <t>2025-05-21T07:47:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingAssociationPrescriptionCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingAssociationPrescriptionCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:22+00:00</t>
+    <t>2025-05-21T07:47:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingAssociationPrescriptionCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingAssociationPrescriptionCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:47:53+00:00</t>
+    <t>2025-05-21T07:49:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingAssociationPrescriptionCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingAssociationPrescriptionCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:49:53+00:00</t>
+    <t>2025-05-21T07:50:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingAssociationPrescriptionCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingAssociationPrescriptionCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:50:26+00:00</t>
+    <t>2025-05-21T07:51:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingAssociationPrescriptionCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingAssociationPrescriptionCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:51:14+00:00</t>
+    <t>2025-05-21T07:52:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/htr-Mapping-CDA-FHIR/ig/mappingAssociationPrescriptionCDAFHIR.xlsx
+++ b/htr-Mapping-CDA-FHIR/ig/mappingAssociationPrescriptionCDAFHIR.xlsx
@@ -58,7 +58,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-05-21T07:52:53+00:00</t>
+    <t>2025-05-21T08:04:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -83,7 +83,7 @@
   </si>
   <si>
     <t>Ce ConceptMap présente deux groupes de mapping : 
- - Groupe Mapping 1 : entre le modèle métier de l'association du document à une prescription et l'élément CDA inFulfillmentOf
+ - Mapping 1 : entre le modèle métier "prescription" et l'élément CDA "inFulfillmentOf"
  - Groupe Mapping 2 : entre l'élément CDA inFulfillmentOf et l'extension FHIR OrderExtension</t>
   </si>
   <si>
